--- a/samples/monthly_report/월간실적_영업팀.xlsx
+++ b/samples/monthly_report/월간실적_영업팀.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -57,7 +54,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -424,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,43 +433,56 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>목표</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>실적</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>부서</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>월</t>
-        </is>
+          <t>영업팀</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>목표</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>실적</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
+          <t>매출액(백만원)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1196.2</v>
       </c>
     </row>
     <row r="3">
@@ -486,14 +496,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>매출액(백만원)</t>
+          <t>신규고객수</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1200</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>1196.2</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>목표 재검토 필요</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -507,14 +522,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>신규고객수</t>
+          <t>수주건수</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>8.800000000000001</v>
+        <v>45</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -533,16 +545,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>수주건수</t>
+          <t>견적건수</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>목표 재검토 필요</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="E5" t="n">
+        <v>129.9</v>
       </c>
     </row>
     <row r="6">
@@ -556,14 +566,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>견적건수</t>
+          <t>고객방문수</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>129.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="7">
@@ -577,14 +587,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>고객방문수</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>60</v>
+          <t>매출채권회수율(%)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>56.2</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -598,16 +610,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>매출채권회수율(%)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
+          <t>수주잔고(백만원)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3000</v>
       </c>
       <c r="E8" t="n">
-        <v>97.90000000000001</v>
+        <v>2996.8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>목표 재검토 필요</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -621,25 +636,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>수주잔고(백만원)</t>
+          <t>고객클레임건수</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2996.8</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>목표 재검토 필요</t>
-        </is>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>영업팀</t>
+          <t>영업 팀</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -647,20 +657,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>고객클레임건수</t>
+          <t>신제품매출(백만원)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7</v>
+        <v>153.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>전월 대비 개선</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>영업 팀</t>
+          <t>영업팀</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -668,19 +683,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>신제품매출(백만원)</t>
+          <t>해외매출(백만원)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E11" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>전월 대비 개선</t>
-        </is>
+        <v>405.1</v>
       </c>
     </row>
     <row r="12">
@@ -694,34 +704,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>해외매출(백만원)</t>
+          <t>영업이익률(%)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>400</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>405.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>영업팀</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>영업이익률(%)</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" t="n">
         <v>8.199999999999999</v>
       </c>
     </row>
